--- a/tools/importer/reports/import-hub-landing-page.report.xlsx
+++ b/tools/importer/reports/import-hub-landing-page.report.xlsx
@@ -73,7 +73,7 @@
     <t>wknd/adventures.report.json</t>
   </si>
   <si>
-    <t>["hero-full","columns-featured","tabs-activity","columns-editorial","cards-article","columns-promo"]</t>
+    <t>["hero","hero","columns-featured","tabs-activity","columns-numbered","cards-article","columns-promo"]</t>
   </si>
   <si>
     <t>wknd/adventures</t>
@@ -82,7 +82,7 @@
     <t>hub-landing-page</t>
   </si>
   <si>
-    <t>2026-03-25T22:41:25.004Z</t>
+    <t>2026-03-26T11:03:25.437Z</t>
   </si>
   <si>
     <t>Adventures — WKND Adventures</t>
@@ -138,13 +138,13 @@
     <t>wknd/destinations.report.json</t>
   </si>
   <si>
-    <t>["hero-full","columns-featured","columns-editorial","cards-article","cards-article","cards-article","cards-article","cards-article","columns-promo"]</t>
+    <t>["hero","columns-featured","columns-numbered","cards-article","cards-article","cards-article","cards-article","cards-article","columns-promo"]</t>
   </si>
   <si>
     <t>wknd/destinations</t>
   </si>
   <si>
-    <t>2026-03-25T23:40:03.762Z</t>
+    <t>2026-03-26T11:03:34.089Z</t>
   </si>
   <si>
     <t>Destinations — WKND Adventures</t>
@@ -153,13 +153,13 @@
     <t>wknd/expeditions.report.json</t>
   </si>
   <si>
-    <t>["hero-full","tabs-activity","columns-editorial","columns-editorial","cards-article","columns-promo"]</t>
+    <t>["hero","tabs-activity","columns-numbered","columns-numbered","cards-article","columns-promo"]</t>
   </si>
   <si>
     <t>wknd/expeditions</t>
   </si>
   <si>
-    <t>2026-03-25T23:43:49.103Z</t>
+    <t>2026-03-26T11:03:29.013Z</t>
   </si>
   <si>
     <t>Expeditions — WKND Adventures</t>
@@ -207,13 +207,13 @@
     <t>wknd/gear.report.json</t>
   </si>
   <si>
-    <t>["hero-full","columns-featured","tabs-activity","columns-editorial","cards-article","cards-article","cards-article","cards-article","cards-article"]</t>
+    <t>["hero","columns-featured","tabs-activity","columns-numbered","cards-article","cards-article","cards-article","cards-article","cards-article"]</t>
   </si>
   <si>
     <t>wknd/gear</t>
   </si>
   <si>
-    <t>2026-03-25T23:43:54.566Z</t>
+    <t>2026-03-26T11:03:37.772Z</t>
   </si>
   <si>
     <t>Gear — WKND Adventures</t>
@@ -225,7 +225,7 @@
     <t>wknd/index.report.json</t>
   </si>
   <si>
-    <t>["hero-full","columns-featured","tabs-activity","ticker","accordion-faq","columns-editorial","columns-gallery"]</t>
+    <t>["hero","hero","columns-featured","tabs-activity","ticker","accordion-faq","columns-numbered","columns-gallery"]</t>
   </si>
   <si>
     <t>wknd/index</t>
@@ -234,7 +234,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-03-25T22:41:22.075Z</t>
+    <t>2026-03-26T11:02:57.847Z</t>
   </si>
   <si>
     <t>WKND Adventures — Bold Stories. Real Life. Wild Places.</t>
@@ -246,13 +246,13 @@
     <t>wknd/sustainability.report.json</t>
   </si>
   <si>
-    <t>["hero-full","columns-featured"]</t>
+    <t>["hero","columns-featured","columns-numbered"]</t>
   </si>
   <si>
     <t>wknd/sustainability</t>
   </si>
   <si>
-    <t>2026-03-25T22:41:49.063Z</t>
+    <t>2026-03-26T00:18:54.671Z</t>
   </si>
   <si>
     <t>Wild Ethics — WKND Adventures</t>
@@ -273,7 +273,7 @@
     <t>blog-article</t>
   </si>
   <si>
-    <t>2026-03-25T22:38:32.623Z</t>
+    <t>2026-03-26T11:03:08.529Z</t>
   </si>
   <si>
     <t>Six Days Through the High Alps — WKND Adventures</t>
@@ -288,7 +288,7 @@
     <t>wknd/blog/kayaking-norway</t>
   </si>
   <si>
-    <t>2026-03-25T22:38:28.755Z</t>
+    <t>2026-03-26T11:03:04.968Z</t>
   </si>
   <si>
     <t>Lofoten Islands: Arctic Surfing at the Top of the World — WKND Adventures</t>
@@ -303,7 +303,7 @@
     <t>wknd/blog/mountain-photography</t>
   </si>
   <si>
-    <t>2026-03-25T22:38:41.925Z</t>
+    <t>2026-03-26T11:03:17.871Z</t>
   </si>
   <si>
     <t>The Camera on Your Back — WKND Adventures</t>
@@ -318,7 +318,7 @@
     <t>wknd/blog/patagonia-trek</t>
   </si>
   <si>
-    <t>2026-03-25T22:38:25.204Z</t>
+    <t>2026-03-26T11:03:00.842Z</t>
   </si>
   <si>
     <t>W Circuit: 9 Days, 115 km — WKND Adventures</t>
@@ -333,7 +333,7 @@
     <t>wknd/blog/ultralight-backpacking</t>
   </si>
   <si>
-    <t>2026-03-25T22:38:45.800Z</t>
+    <t>2026-03-26T11:03:21.742Z</t>
   </si>
   <si>
     <t>Sub-10 lb: What to Cut, What to Keep — WKND Adventures</t>
@@ -348,7 +348,7 @@
     <t>wknd/blog/yosemite-rock-climbing</t>
   </si>
   <si>
-    <t>2026-03-25T22:38:37.044Z</t>
+    <t>2026-03-26T11:03:13.041Z</t>
   </si>
   <si>
     <t>First Light on the Valley — WKND Adventures</t>
